--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N153_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N153_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.70662174395687</v>
+        <v>10.02732603339299</v>
       </c>
       <c r="D2" t="n">
-        <v>62.54108342118471</v>
+        <v>10.16292605594252</v>
       </c>
       <c r="E2" t="n">
-        <v>19.31548816759264</v>
+        <v>3.138766827233805</v>
       </c>
       <c r="F2" t="n">
-        <v>19.65279564315424</v>
+        <v>3.193579292012565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.49020849777863</v>
+        <v>9.829658880889028</v>
       </c>
       <c r="D3" t="n">
-        <v>60.26039898199384</v>
+        <v>9.792314834573999</v>
       </c>
       <c r="E3" t="n">
-        <v>19.31548816759264</v>
+        <v>3.138766827233805</v>
       </c>
       <c r="F3" t="n">
-        <v>19.65279564315424</v>
+        <v>3.193579292012565</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.46924843276994</v>
+        <v>3.813752870325116</v>
       </c>
       <c r="D4" t="n">
-        <v>23.1786253861114</v>
+        <v>3.766526625243103</v>
       </c>
       <c r="E4" t="n">
-        <v>19.31548816759264</v>
+        <v>3.138766827233805</v>
       </c>
       <c r="F4" t="n">
-        <v>19.65279564315424</v>
+        <v>3.193579292012565</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.53331806304478</v>
+        <v>3.499164185244777</v>
       </c>
       <c r="D5" t="n">
-        <v>21.13125533757717</v>
+        <v>3.43382899235629</v>
       </c>
       <c r="E5" t="n">
-        <v>19.31548816759264</v>
+        <v>3.138766827233805</v>
       </c>
       <c r="F5" t="n">
-        <v>19.65279564315424</v>
+        <v>3.193579292012565</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
